--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132009422</v>
+        <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>99257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514154</v>
+        <v>513963</v>
       </c>
       <c r="R2" t="n">
-        <v>6757482</v>
+        <v>6757728</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +757,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,33 +786,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009422</t>
+          <t>https://artportalen.se/Sighting/136799214</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132009538</v>
+        <v>132009422</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,31 +821,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -880,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,51 +925,60 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009538</t>
+          <t>https://artportalen.se/Sighting/132009422</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837931</v>
+        <v>132009538</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514125</v>
+        <v>514154</v>
       </c>
       <c r="R4" t="n">
-        <v>6757521</v>
+        <v>6757482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,12 +1005,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,74 +1035,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837931</t>
+          <t>https://artportalen.se/Sighting/132009538</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132011346</v>
+        <v>136795146</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514102</v>
+        <v>514120</v>
       </c>
       <c r="R5" t="n">
-        <v>6757458</v>
+        <v>6757473</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,70 +1147,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132011346</t>
+          <t>https://artportalen.se/Sighting/136795146</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132008652</v>
+        <v>136795147</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514007</v>
+        <v>514131</v>
       </c>
       <c r="R6" t="n">
-        <v>6757453</v>
+        <v>6757522</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,49 +1259,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008652</t>
+          <t>https://artportalen.se/Sighting/136795147</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126837973</v>
+        <v>136795148</v>
       </c>
       <c r="B7" t="n">
-        <v>8444</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,13 +1311,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514178</v>
+        <v>514144</v>
       </c>
       <c r="R7" t="n">
-        <v>6757557</v>
+        <v>6757511</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,12 +1341,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,49 +1371,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837973</t>
+          <t>https://artportalen.se/Sighting/136795148</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126837950</v>
+        <v>136795150</v>
       </c>
       <c r="B8" t="n">
-        <v>99153</v>
+        <v>92543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514178</v>
+        <v>514175</v>
       </c>
       <c r="R8" t="n">
-        <v>6757313</v>
+        <v>6757565</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,12 +1453,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,49 +1483,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837950</t>
+          <t>https://artportalen.se/Sighting/136795150</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126837967</v>
+        <v>136795153</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>96563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,13 +1535,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514171</v>
+        <v>513896</v>
       </c>
       <c r="R9" t="n">
-        <v>6757320</v>
+        <v>6757662</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,12 +1565,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,74 +1595,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837967</t>
+          <t>https://artportalen.se/Sighting/136795153</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132008521</v>
+        <v>136795155</v>
       </c>
       <c r="B10" t="n">
-        <v>99195</v>
+        <v>96563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514007</v>
+        <v>513959</v>
       </c>
       <c r="R10" t="n">
-        <v>6757453</v>
+        <v>6757723</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,22 +1677,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,71 +1707,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008521</t>
+          <t>https://artportalen.se/Sighting/136795155</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132009294</v>
+        <v>136795159</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>96563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514154</v>
+        <v>513852</v>
       </c>
       <c r="R11" t="n">
-        <v>6757482</v>
+        <v>6757553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,22 +1789,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,69 +1819,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009294</t>
+          <t>https://artportalen.se/Sighting/136795159</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132009740</v>
+        <v>136799093</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>96563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514174</v>
+        <v>513837</v>
       </c>
       <c r="R12" t="n">
-        <v>6757543</v>
+        <v>6757582</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,22 +1901,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,71 +1931,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009740</t>
+          <t>https://artportalen.se/Sighting/136799093</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132010406</v>
+        <v>126837931</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514098</v>
+        <v>514125</v>
       </c>
       <c r="R13" t="n">
-        <v>6757561</v>
+        <v>6757521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,22 +2013,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,27 +2033,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132010406</t>
+          <t>https://artportalen.se/Sighting/126837931</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132012536</v>
+        <v>132011346</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,26 +2061,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2091,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514113</v>
+        <v>514102</v>
       </c>
       <c r="R14" t="n">
-        <v>6757269</v>
+        <v>6757458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,51 +2165,56 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132012536</t>
+          <t>https://artportalen.se/Sighting/132011346</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013322</v>
+        <v>132008652</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513994</v>
+        <v>514007</v>
       </c>
       <c r="R15" t="n">
-        <v>6757319</v>
+        <v>6757453</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,54 +2282,66 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132013322</t>
+          <t>https://artportalen.se/Sighting/132008652</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126837934</v>
+        <v>136798692</v>
       </c>
       <c r="B16" t="n">
-        <v>104628</v>
+        <v>58169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514224</v>
+        <v>514162</v>
       </c>
       <c r="R16" t="n">
-        <v>6757306</v>
+        <v>6757515</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2345,12 +2365,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,27 +2395,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837934</t>
+          <t>https://artportalen.se/Sighting/136798692</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126837969</v>
+        <v>136795161</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>58164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,21 +2423,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514019</v>
+        <v>513993</v>
       </c>
       <c r="R17" t="n">
-        <v>6757359</v>
+        <v>6757411</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,12 +2477,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,27 +2507,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837969</t>
+          <t>https://artportalen.se/Sighting/136795161</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126837972</v>
+        <v>136798682</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>8463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2519,13 +2559,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514153</v>
+        <v>514058</v>
       </c>
       <c r="R18" t="n">
-        <v>6757646</v>
+        <v>6757263</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2549,12 +2589,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,27 +2619,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837972</t>
+          <t>https://artportalen.se/Sighting/136798682</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132008409</v>
+        <v>126837973</v>
       </c>
       <c r="B19" t="n">
-        <v>101403</v>
+        <v>8444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,43 +2647,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514007</v>
+        <v>514178</v>
       </c>
       <c r="R19" t="n">
-        <v>6757453</v>
+        <v>6757557</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,22 +2701,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,27 +2721,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008409</t>
+          <t>https://artportalen.se/Sighting/126837973</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132009025</v>
+        <v>126837950</v>
       </c>
       <c r="B20" t="n">
-        <v>101403</v>
+        <v>99153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,38 +2749,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514069</v>
+        <v>514178</v>
       </c>
       <c r="R20" t="n">
-        <v>6757477</v>
+        <v>6757313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,22 +2803,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,62 +2823,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009025</t>
+          <t>https://artportalen.se/Sighting/126837950</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013399</v>
+        <v>126837967</v>
       </c>
       <c r="B21" t="n">
-        <v>101403</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513994</v>
+        <v>514171</v>
       </c>
       <c r="R21" t="n">
-        <v>6757319</v>
+        <v>6757320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,22 +2905,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,18 +2925,4368 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126837967</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132008521</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>514007</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6757453</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132008521</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132009294</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>514154</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6757482</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009294</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132009740</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514174</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6757543</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009740</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132010406</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>514098</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6757561</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132010406</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132012536</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>514113</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6757269</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132012536</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132013322</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>513994</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6757319</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013322</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136795149</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>514167</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6757542</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795149</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136795151</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>514179</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6757570</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795151</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136798685</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>514094</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6757495</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>4 blomställningar 4 bladroserrer</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798685</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136798686</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>514118</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6757538</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 blom 6 blad</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798686</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136798687</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>514114</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6757542</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 överblommade ståndare 15 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798687</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136798689</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>514173</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6757591</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 böadrosetter</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798689</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136798690</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>514168</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6757541</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798690</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136798691</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>514161</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6757513</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798691</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136798693</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>514153</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6757506</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>100st på 2 m2</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798693</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136798694</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>514120</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6757531</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798694</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136798695</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>514133</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6757538</v>
+      </c>
+      <c r="S38" t="n">
+        <v>13</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136798696</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>514133</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6757547</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798696</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136798697</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>514145</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6757586</v>
+      </c>
+      <c r="S40" t="n">
+        <v>12</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>15 badrosetter</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798697</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136795154</v>
+      </c>
+      <c r="B41" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>513942</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6757692</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795154</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136795156</v>
+      </c>
+      <c r="B42" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>513937</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6757667</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795156</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136795157</v>
+      </c>
+      <c r="B43" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>513908</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6757637</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795157</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126837934</v>
+      </c>
+      <c r="B44" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>514224</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6757306</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837934</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126837969</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>514019</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6757359</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837969</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126837972</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>514153</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6757646</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837972</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132008409</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>514007</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6757453</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132008409</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132009025</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>514069</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6757477</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132009025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132013399</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lintjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>513994</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6757319</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132013399</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136795145</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>514123</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6757409</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795145</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136795152</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>514149</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6757621</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795152</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136795158</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>513852</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6757553</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136795158</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136798683</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>514083</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6757414</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798683</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136798688</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>514125</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6757625</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798688</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136798698</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>514148</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6757596</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798698</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136799092</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>513831</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6757584</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799092</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136799212</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99157</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>513868</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6757642</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799212</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136799215</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99157</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>513929</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6757710</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799215</t>
         </is>
       </c>
     </row>
@@ -2955,6 +7312,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99257</v>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>136795146</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136795147</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136795148</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>136795150</v>
       </c>
       <c r="B8" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136795153</v>
       </c>
       <c r="B9" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>136795155</v>
       </c>
       <c r="B10" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>136795159</v>
       </c>
       <c r="B11" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>136799093</v>
       </c>
       <c r="B12" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>136795149</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>136795151</v>
       </c>
       <c r="B29" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>136798685</v>
       </c>
       <c r="B30" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>136798686</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>136798687</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136798689</v>
       </c>
       <c r="B33" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>136798690</v>
       </c>
       <c r="B34" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136798691</v>
       </c>
       <c r="B35" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>136798693</v>
       </c>
       <c r="B36" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>136798694</v>
       </c>
       <c r="B37" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>136798695</v>
       </c>
       <c r="B38" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136798696</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>136798697</v>
       </c>
       <c r="B40" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136795154</v>
       </c>
       <c r="B41" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>136795156</v>
       </c>
       <c r="B42" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>136795157</v>
       </c>
       <c r="B43" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>136795145</v>
       </c>
       <c r="B50" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>136795152</v>
       </c>
       <c r="B51" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>136795158</v>
       </c>
       <c r="B52" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>136798683</v>
       </c>
       <c r="B53" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>136798688</v>
       </c>
       <c r="B54" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>136798698</v>
       </c>
       <c r="B55" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>136799092</v>
       </c>
       <c r="B56" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>136799212</v>
       </c>
       <c r="B57" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>136799215</v>
       </c>
       <c r="B58" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,57 +810,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132009422</v>
+        <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>99259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514154</v>
+        <v>513861</v>
       </c>
       <c r="R3" t="n">
-        <v>6757482</v>
+        <v>6757543</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,27 +895,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009422</t>
+          <t>https://artportalen.se/Sighting/136933180</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132009538</v>
+        <v>132009422</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,31 +927,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1010,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,16 +1031,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009538</t>
+          <t>https://artportalen.se/Sighting/132009422</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136795146</v>
+        <v>132009538</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,20 +1065,29 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514120</v>
+        <v>514154</v>
       </c>
       <c r="R5" t="n">
-        <v>6757473</v>
+        <v>6757482</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1111,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,24 +1141,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795146</t>
+          <t>https://artportalen.se/Sighting/132009538</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136795147</v>
+        <v>136795146</v>
       </c>
       <c r="B6" t="n">
         <v>92113</v>
@@ -1199,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514131</v>
+        <v>514120</v>
       </c>
       <c r="R6" t="n">
-        <v>6757522</v>
+        <v>6757473</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,13 +1264,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795147</t>
+          <t>https://artportalen.se/Sighting/136795146</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136795148</v>
+        <v>136795147</v>
       </c>
       <c r="B7" t="n">
         <v>92113</v>
@@ -1311,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514144</v>
+        <v>514131</v>
       </c>
       <c r="R7" t="n">
-        <v>6757511</v>
+        <v>6757522</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,16 +1376,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795148</t>
+          <t>https://artportalen.se/Sighting/136795147</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136795150</v>
+        <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92545</v>
+        <v>92113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514175</v>
+        <v>514144</v>
       </c>
       <c r="R8" t="n">
-        <v>6757565</v>
+        <v>6757511</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1458,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,38 +1488,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795150</t>
+          <t>https://artportalen.se/Sighting/136795148</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136795153</v>
+        <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>96565</v>
+        <v>92545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2812</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1535,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513896</v>
+        <v>514175</v>
       </c>
       <c r="R9" t="n">
-        <v>6757662</v>
+        <v>6757565</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,13 +1600,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795153</t>
+          <t>https://artportalen.se/Sighting/136795150</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136795155</v>
+        <v>136795153</v>
       </c>
       <c r="B10" t="n">
         <v>96565</v>
@@ -1647,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513959</v>
+        <v>513896</v>
       </c>
       <c r="R10" t="n">
-        <v>6757723</v>
+        <v>6757662</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,13 +1712,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795155</t>
+          <t>https://artportalen.se/Sighting/136795153</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136795159</v>
+        <v>136795155</v>
       </c>
       <c r="B11" t="n">
         <v>96565</v>
@@ -1759,13 +1753,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513852</v>
+        <v>513959</v>
       </c>
       <c r="R11" t="n">
-        <v>6757553</v>
+        <v>6757723</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,13 +1824,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795159</t>
+          <t>https://artportalen.se/Sighting/136795155</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136799093</v>
+        <v>136795159</v>
       </c>
       <c r="B12" t="n">
         <v>96565</v>
@@ -1871,13 +1865,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513837</v>
+        <v>513852</v>
       </c>
       <c r="R12" t="n">
-        <v>6757582</v>
+        <v>6757553</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,22 +1895,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,27 +1925,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799093</t>
+          <t>https://artportalen.se/Sighting/136795159</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837931</v>
+        <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>91872</v>
+        <v>96565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514125</v>
+        <v>513837</v>
       </c>
       <c r="R13" t="n">
-        <v>6757521</v>
+        <v>6757582</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,12 +2007,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,71 +2037,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837931</t>
+          <t>https://artportalen.se/Sighting/136799093</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132011346</v>
+        <v>126837931</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514102</v>
+        <v>514125</v>
       </c>
       <c r="R14" t="n">
-        <v>6757458</v>
+        <v>6757521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,22 +2119,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,55 +2139,59 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132011346</t>
+          <t>https://artportalen.se/Sighting/126837931</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132008652</v>
+        <v>132011346</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2211,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514007</v>
+        <v>514102</v>
       </c>
       <c r="R15" t="n">
-        <v>6757453</v>
+        <v>6757458</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2245,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,66 +2271,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008652</t>
+          <t>https://artportalen.se/Sighting/132011346</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136798692</v>
+        <v>132008652</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514162</v>
+        <v>514007</v>
       </c>
       <c r="R16" t="n">
-        <v>6757515</v>
+        <v>6757453</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2365,22 +2347,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,65 +2377,77 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798692</t>
+          <t>https://artportalen.se/Sighting/132008652</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136795161</v>
+        <v>136798692</v>
       </c>
       <c r="B17" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513993</v>
+        <v>514162</v>
       </c>
       <c r="R17" t="n">
-        <v>6757411</v>
+        <v>6757515</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,22 +2471,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,27 +2501,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795161</t>
+          <t>https://artportalen.se/Sighting/136798692</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136798682</v>
+        <v>136795161</v>
       </c>
       <c r="B18" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,21 +2529,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2559,13 +2553,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514058</v>
+        <v>513993</v>
       </c>
       <c r="R18" t="n">
-        <v>6757263</v>
+        <v>6757411</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2589,22 +2583,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,27 +2613,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798682</t>
+          <t>https://artportalen.se/Sighting/136795161</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126837973</v>
+        <v>136798682</v>
       </c>
       <c r="B19" t="n">
-        <v>8444</v>
+        <v>8463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,21 +2641,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2671,13 +2665,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514178</v>
+        <v>514058</v>
       </c>
       <c r="R19" t="n">
-        <v>6757557</v>
+        <v>6757263</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,12 +2695,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,27 +2725,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837973</t>
+          <t>https://artportalen.se/Sighting/136798682</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837950</v>
+        <v>126837973</v>
       </c>
       <c r="B20" t="n">
-        <v>99153</v>
+        <v>8444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,21 +2753,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2776,7 +2780,7 @@
         <v>514178</v>
       </c>
       <c r="R20" t="n">
-        <v>6757313</v>
+        <v>6757557</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2834,38 +2838,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837950</t>
+          <t>https://artportalen.se/Sighting/126837973</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126837967</v>
+        <v>126837950</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2875,10 +2879,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514171</v>
+        <v>514178</v>
       </c>
       <c r="R21" t="n">
-        <v>6757320</v>
+        <v>6757313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,63 +2940,62 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837967</t>
+          <t>https://artportalen.se/Sighting/126837950</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132008521</v>
+        <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99388</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514007</v>
+        <v>513908</v>
       </c>
       <c r="R22" t="n">
-        <v>6757453</v>
+        <v>6757597</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,22 +3019,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,33 +3033,38 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008521</t>
+          <t>https://artportalen.se/Sighting/136936654</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132009294</v>
+        <v>126837967</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,26 +3089,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514154</v>
+        <v>514171</v>
       </c>
       <c r="R23" t="n">
-        <v>6757482</v>
+        <v>6757320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3137,22 +3126,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3167,24 +3146,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009294</t>
+          <t>https://artportalen.se/Sighting/126837967</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132009740</v>
+        <v>132008521</v>
       </c>
       <c r="B24" t="n">
         <v>99195</v>
@@ -3214,7 +3193,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3223,10 +3207,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514174</v>
+        <v>514007</v>
       </c>
       <c r="R24" t="n">
-        <v>6757543</v>
+        <v>6757453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3258,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3252,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,13 +3278,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009740</t>
+          <t>https://artportalen.se/Sighting/132008521</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132010406</v>
+        <v>132009294</v>
       </c>
       <c r="B25" t="n">
         <v>99195</v>
@@ -3330,7 +3314,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3344,10 +3328,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514098</v>
+        <v>514154</v>
       </c>
       <c r="R25" t="n">
-        <v>6757561</v>
+        <v>6757482</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,13 +3399,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132010406</t>
+          <t>https://artportalen.se/Sighting/132009294</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132012536</v>
+        <v>132009740</v>
       </c>
       <c r="B26" t="n">
         <v>99195</v>
@@ -3451,12 +3435,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3465,10 +3444,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514113</v>
+        <v>514174</v>
       </c>
       <c r="R26" t="n">
-        <v>6757269</v>
+        <v>6757543</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3500,7 +3479,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3510,7 +3489,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3536,13 +3515,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132012536</t>
+          <t>https://artportalen.se/Sighting/132009740</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013322</v>
+        <v>132010406</v>
       </c>
       <c r="B27" t="n">
         <v>99195</v>
@@ -3570,17 +3549,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513994</v>
+        <v>514098</v>
       </c>
       <c r="R27" t="n">
-        <v>6757319</v>
+        <v>6757561</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,7 +3600,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3610,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,16 +3636,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132013322</t>
+          <t>https://artportalen.se/Sighting/132010406</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136795149</v>
+        <v>132012536</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3672,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3694,17 +3682,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514167</v>
+        <v>514113</v>
       </c>
       <c r="R28" t="n">
-        <v>6757542</v>
+        <v>6757269</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3728,22 +3716,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,27 +3746,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795149</t>
+          <t>https://artportalen.se/Sighting/132012536</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136795151</v>
+        <v>132013322</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3803,29 +3791,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514179</v>
+        <v>513994</v>
       </c>
       <c r="R29" t="n">
-        <v>6757570</v>
+        <v>6757319</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3849,22 +3828,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3879,24 +3858,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795151</t>
+          <t>https://artportalen.se/Sighting/132013322</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136798685</v>
+        <v>136795149</v>
       </c>
       <c r="B30" t="n">
         <v>99353</v>
@@ -3926,7 +3905,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3934,23 +3913,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514094</v>
+        <v>514167</v>
       </c>
       <c r="R30" t="n">
-        <v>6757495</v>
+        <v>6757542</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3977,27 +3949,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>4 blomställningar 4 bladroserrer</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4006,31 +3973,30 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798685</t>
+          <t>https://artportalen.se/Sighting/136795149</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136798686</v>
+        <v>136795151</v>
       </c>
       <c r="B31" t="n">
         <v>99353</v>
@@ -4058,20 +4024,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514118</v>
+        <v>514179</v>
       </c>
       <c r="R31" t="n">
-        <v>6757538</v>
+        <v>6757570</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4095,27 +4070,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2 blom 6 blad</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4130,24 +4100,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798686</t>
+          <t>https://artportalen.se/Sighting/136795151</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136798687</v>
+        <v>136798685</v>
       </c>
       <c r="B32" t="n">
         <v>99353</v>
@@ -4177,10 +4147,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -4194,10 +4168,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514114</v>
+        <v>514094</v>
       </c>
       <c r="R32" t="n">
-        <v>6757542</v>
+        <v>6757495</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4229,7 +4203,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4239,12 +4213,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2 överblommade ståndare 15 bladrosetter</t>
+          <t>4 blomställningar 4 bladroserrer</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,13 +4245,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798687</t>
+          <t>https://artportalen.se/Sighting/136798685</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136798689</v>
+        <v>136798686</v>
       </c>
       <c r="B33" t="n">
         <v>99353</v>
@@ -4305,32 +4279,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514173</v>
+        <v>514118</v>
       </c>
       <c r="R33" t="n">
-        <v>6757591</v>
+        <v>6757538</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4359,7 +4321,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4369,12 +4331,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>4 böadrosetter</t>
+          <t>2 blom 6 blad</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4383,7 +4345,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4401,13 +4362,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798689</t>
+          <t>https://artportalen.se/Sighting/136798686</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136798690</v>
+        <v>136798687</v>
       </c>
       <c r="B34" t="n">
         <v>99353</v>
@@ -4437,13 +4398,13 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4454,10 +4415,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514168</v>
+        <v>514114</v>
       </c>
       <c r="R34" t="n">
-        <v>6757541</v>
+        <v>6757542</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4489,7 +4450,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4499,12 +4460,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>2 överblommade ståndare 15 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4531,13 +4492,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798690</t>
+          <t>https://artportalen.se/Sighting/136798687</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136798691</v>
+        <v>136798689</v>
       </c>
       <c r="B35" t="n">
         <v>99353</v>
@@ -4567,7 +4528,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4584,13 +4545,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514161</v>
+        <v>514173</v>
       </c>
       <c r="R35" t="n">
-        <v>6757513</v>
+        <v>6757591</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4619,7 +4580,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4629,12 +4590,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>4 böadrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4661,13 +4622,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798691</t>
+          <t>https://artportalen.se/Sighting/136798689</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136798693</v>
+        <v>136798690</v>
       </c>
       <c r="B36" t="n">
         <v>99353</v>
@@ -4697,14 +4658,10 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4718,10 +4675,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514153</v>
+        <v>514168</v>
       </c>
       <c r="R36" t="n">
-        <v>6757506</v>
+        <v>6757541</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4753,7 +4710,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4763,12 +4720,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>100st på 2 m2</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4795,13 +4752,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798693</t>
+          <t>https://artportalen.se/Sighting/136798690</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136798694</v>
+        <v>136798691</v>
       </c>
       <c r="B37" t="n">
         <v>99353</v>
@@ -4829,20 +4786,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514120</v>
+        <v>514161</v>
       </c>
       <c r="R37" t="n">
-        <v>6757531</v>
+        <v>6757513</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4866,27 +4835,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4895,6 +4864,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4912,13 +4882,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798694</t>
+          <t>https://artportalen.se/Sighting/136798691</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136798695</v>
+        <v>136798693</v>
       </c>
       <c r="B38" t="n">
         <v>99353</v>
@@ -4946,8 +4916,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -4956,13 +4939,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514133</v>
+        <v>514153</v>
       </c>
       <c r="R38" t="n">
-        <v>6757538</v>
+        <v>6757506</v>
       </c>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4986,22 +4969,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>100st på 2 m2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5028,13 +5016,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798695</t>
+          <t>https://artportalen.se/Sighting/136798693</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136798696</v>
+        <v>136798694</v>
       </c>
       <c r="B39" t="n">
         <v>99353</v>
@@ -5062,32 +5050,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514133</v>
+        <v>514120</v>
       </c>
       <c r="R39" t="n">
-        <v>6757547</v>
+        <v>6757531</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5116,7 +5092,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5126,7 +5102,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5135,7 +5116,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5153,13 +5133,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798696</t>
+          <t>https://artportalen.se/Sighting/136798694</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136798697</v>
+        <v>136798695</v>
       </c>
       <c r="B40" t="n">
         <v>99353</v>
@@ -5187,21 +5167,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -5210,13 +5177,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514145</v>
+        <v>514133</v>
       </c>
       <c r="R40" t="n">
-        <v>6757586</v>
+        <v>6757538</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5245,7 +5212,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5255,12 +5222,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>15 badrosetter</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5287,54 +5249,66 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798697</t>
+          <t>https://artportalen.se/Sighting/136798695</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136795154</v>
+        <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>103928</v>
+        <v>99353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513942</v>
+        <v>514133</v>
       </c>
       <c r="R41" t="n">
-        <v>6757692</v>
+        <v>6757547</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5363,7 +5337,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5373,7 +5347,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5382,71 +5356,88 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795154</t>
+          <t>https://artportalen.se/Sighting/136798696</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136795156</v>
+        <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>103928</v>
+        <v>99353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513937</v>
+        <v>514145</v>
       </c>
       <c r="R42" t="n">
-        <v>6757667</v>
+        <v>6757586</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5475,7 +5466,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5485,7 +5476,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>15 badrosetter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5494,30 +5490,31 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795156</t>
+          <t>https://artportalen.se/Sighting/136798697</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136795157</v>
+        <v>136795154</v>
       </c>
       <c r="B43" t="n">
         <v>103928</v>
@@ -5552,13 +5549,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513908</v>
+        <v>513942</v>
       </c>
       <c r="R43" t="n">
-        <v>6757637</v>
+        <v>6757692</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5587,7 +5584,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5597,7 +5594,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5623,16 +5620,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795157</t>
+          <t>https://artportalen.se/Sighting/136795154</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126837934</v>
+        <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>104628</v>
+        <v>103928</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5640,16 +5637,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5664,13 +5661,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514224</v>
+        <v>513937</v>
       </c>
       <c r="R44" t="n">
-        <v>6757306</v>
+        <v>6757667</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5694,12 +5691,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,27 +5721,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837934</t>
+          <t>https://artportalen.se/Sighting/136795156</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126837969</v>
+        <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>101326</v>
+        <v>103928</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5742,21 +5749,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5766,13 +5773,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514019</v>
+        <v>513908</v>
       </c>
       <c r="R45" t="n">
-        <v>6757359</v>
+        <v>6757637</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5796,12 +5803,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5816,27 +5833,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837969</t>
+          <t>https://artportalen.se/Sighting/136795157</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126837972</v>
+        <v>126837934</v>
       </c>
       <c r="B46" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5844,21 +5861,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,10 +5885,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514153</v>
+        <v>514224</v>
       </c>
       <c r="R46" t="n">
-        <v>6757646</v>
+        <v>6757306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5929,16 +5946,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837972</t>
+          <t>https://artportalen.se/Sighting/126837934</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132008409</v>
+        <v>126837969</v>
       </c>
       <c r="B47" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5963,26 +5980,17 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514007</v>
+        <v>514019</v>
       </c>
       <c r="R47" t="n">
-        <v>6757453</v>
+        <v>6757359</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6009,22 +6017,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6039,27 +6037,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008409</t>
+          <t>https://artportalen.se/Sighting/126837969</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132009025</v>
+        <v>126837972</v>
       </c>
       <c r="B48" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6084,21 +6082,17 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514069</v>
+        <v>514153</v>
       </c>
       <c r="R48" t="n">
-        <v>6757477</v>
+        <v>6757646</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6125,22 +6119,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6155,24 +6139,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009025</t>
+          <t>https://artportalen.se/Sighting/126837972</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013399</v>
+        <v>132008409</v>
       </c>
       <c r="B49" t="n">
         <v>101403</v>
@@ -6200,17 +6184,26 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513994</v>
+        <v>514007</v>
       </c>
       <c r="R49" t="n">
-        <v>6757319</v>
+        <v>6757453</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6242,7 +6235,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6252,7 +6245,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6278,16 +6271,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132013399</t>
+          <t>https://artportalen.se/Sighting/132008409</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136795145</v>
+        <v>132009025</v>
       </c>
       <c r="B50" t="n">
-        <v>101563</v>
+        <v>101403</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6312,20 +6305,24 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514123</v>
+        <v>514069</v>
       </c>
       <c r="R50" t="n">
-        <v>6757409</v>
+        <v>6757477</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6349,22 +6346,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6379,27 +6376,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795145</t>
+          <t>https://artportalen.se/Sighting/132009025</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136795152</v>
+        <v>132013399</v>
       </c>
       <c r="B51" t="n">
-        <v>101563</v>
+        <v>101403</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6427,17 +6424,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514149</v>
+        <v>513994</v>
       </c>
       <c r="R51" t="n">
-        <v>6757621</v>
+        <v>6757319</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6461,22 +6458,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6491,24 +6488,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795152</t>
+          <t>https://artportalen.se/Sighting/132013399</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136795158</v>
+        <v>136795145</v>
       </c>
       <c r="B52" t="n">
         <v>101563</v>
@@ -6543,13 +6540,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513852</v>
+        <v>514123</v>
       </c>
       <c r="R52" t="n">
-        <v>6757553</v>
+        <v>6757409</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6578,7 +6575,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6588,7 +6585,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6614,13 +6611,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795158</t>
+          <t>https://artportalen.se/Sighting/136795145</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136798683</v>
+        <v>136795152</v>
       </c>
       <c r="B53" t="n">
         <v>101563</v>
@@ -6655,10 +6652,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514083</v>
+        <v>514149</v>
       </c>
       <c r="R53" t="n">
-        <v>6757414</v>
+        <v>6757621</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6685,22 +6682,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6715,24 +6712,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798683</t>
+          <t>https://artportalen.se/Sighting/136795152</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136798688</v>
+        <v>136795158</v>
       </c>
       <c r="B54" t="n">
         <v>101563</v>
@@ -6767,13 +6764,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514125</v>
+        <v>513852</v>
       </c>
       <c r="R54" t="n">
-        <v>6757625</v>
+        <v>6757553</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6797,22 +6794,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6827,24 +6824,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798688</t>
+          <t>https://artportalen.se/Sighting/136795158</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136798698</v>
+        <v>136798683</v>
       </c>
       <c r="B55" t="n">
         <v>101563</v>
@@ -6879,10 +6876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514148</v>
+        <v>514083</v>
       </c>
       <c r="R55" t="n">
-        <v>6757596</v>
+        <v>6757414</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6909,22 +6906,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6950,13 +6947,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798698</t>
+          <t>https://artportalen.se/Sighting/136798683</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136799092</v>
+        <v>136798688</v>
       </c>
       <c r="B56" t="n">
         <v>101563</v>
@@ -6991,10 +6988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513831</v>
+        <v>514125</v>
       </c>
       <c r="R56" t="n">
-        <v>6757584</v>
+        <v>6757625</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7021,22 +7018,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7056,22 +7053,22 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799092</t>
+          <t>https://artportalen.se/Sighting/136798688</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136799212</v>
+        <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>99159</v>
+        <v>101563</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,21 +7076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7103,10 +7100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513868</v>
+        <v>514148</v>
       </c>
       <c r="R57" t="n">
-        <v>6757642</v>
+        <v>6757596</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7133,22 +7130,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7168,22 +7165,22 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799212</t>
+          <t>https://artportalen.se/Sighting/136798698</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136799215</v>
+        <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>99159</v>
+        <v>101563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7191,21 +7188,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7215,13 +7212,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513929</v>
+        <v>513831</v>
       </c>
       <c r="R58" t="n">
-        <v>6757710</v>
+        <v>6757584</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7250,7 +7247,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7260,7 +7257,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7285,6 +7282,230 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799092</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136799212</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>513868</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6757642</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799212</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136799215</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>513929</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6757710</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136799215</t>
         </is>
@@ -7349,6 +7570,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99265</v>
+        <v>99267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99267</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99267</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99274</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99280</v>
+        <v>99282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99282</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99282</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>136798692</v>
       </c>
       <c r="B17" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>136795161</v>
       </c>
       <c r="B18" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>136798692</v>
       </c>
       <c r="B17" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>136795161</v>
       </c>
       <c r="B18" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>136798682</v>
       </c>
       <c r="B19" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -714,11 +714,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -2429,11 +2425,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -4155,11 +4147,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4402,11 +4390,7 @@
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4532,11 +4516,7 @@
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4662,11 +4642,7 @@
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4792,11 +4768,7 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -4926,11 +4898,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -5289,11 +5257,7 @@
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -5418,11 +5382,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99297</v>
+        <v>99300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99297</v>
+        <v>99300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99300</v>
+        <v>99310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99300</v>
+        <v>99310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136798692</v>
       </c>
       <c r="B17" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>136795161</v>
       </c>
       <c r="B18" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>136798682</v>
       </c>
       <c r="B19" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103969</v>
+        <v>103984</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103969</v>
+        <v>103984</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103969</v>
+        <v>103984</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99200</v>
+        <v>99210</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99200</v>
+        <v>99210</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99310</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99310</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103984</v>
+        <v>103985</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103984</v>
+        <v>103985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103984</v>
+        <v>103985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136798692</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>136795161</v>
       </c>
       <c r="B18" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103985</v>
+        <v>103990</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103985</v>
+        <v>103990</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103985</v>
+        <v>103990</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99211</v>
+        <v>99216</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99211</v>
+        <v>99216</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99316</v>
+        <v>99318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99316</v>
+        <v>99318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103990</v>
+        <v>103993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103990</v>
+        <v>103993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103990</v>
+        <v>103993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99216</v>
+        <v>99218</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99216</v>
+        <v>99218</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799214</v>
       </c>
       <c r="B2" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136795146</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136795147</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>136795148</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136795150</v>
       </c>
       <c r="B9" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136795153</v>
       </c>
       <c r="B10" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136795155</v>
       </c>
       <c r="B11" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>136795159</v>
       </c>
       <c r="B12" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136799093</v>
       </c>
       <c r="B13" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>136798692</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>136795161</v>
       </c>
       <c r="B18" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136795149</v>
       </c>
       <c r="B30" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>136795151</v>
       </c>
       <c r="B31" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>136798685</v>
       </c>
       <c r="B32" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136798686</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136798687</v>
       </c>
       <c r="B34" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>136798689</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136798690</v>
       </c>
       <c r="B36" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136798691</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>136798693</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>136798694</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136798695</v>
       </c>
       <c r="B40" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136798696</v>
       </c>
       <c r="B41" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>136798697</v>
       </c>
       <c r="B42" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>136795154</v>
       </c>
       <c r="B43" t="n">
-        <v>103993</v>
+        <v>103999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>136795156</v>
       </c>
       <c r="B44" t="n">
-        <v>103993</v>
+        <v>103999</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>136795157</v>
       </c>
       <c r="B45" t="n">
-        <v>103993</v>
+        <v>103999</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>136795145</v>
       </c>
       <c r="B52" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>136795152</v>
       </c>
       <c r="B53" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136795158</v>
       </c>
       <c r="B54" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>136798683</v>
       </c>
       <c r="B55" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>136798688</v>
       </c>
       <c r="B56" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>136798698</v>
       </c>
       <c r="B57" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136799092</v>
       </c>
       <c r="B58" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136799212</v>
       </c>
       <c r="B59" t="n">
-        <v>99218</v>
+        <v>99224</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136799215</v>
       </c>
       <c r="B60" t="n">
-        <v>99218</v>
+        <v>99224</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99324</v>
+        <v>99336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99336</v>
+        <v>99337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99337</v>
+        <v>99340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136936654</v>
       </c>
       <c r="B22" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99340</v>
+        <v>99341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136798692</v>
+        <v>137520874</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,45 +2401,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Born1, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514162</v>
+        <v>514077</v>
       </c>
       <c r="R17" t="n">
-        <v>6757515</v>
+        <v>6757433</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,22 +2455,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran, födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,65 +2490,73 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798692</t>
+          <t>https://artportalen.se/Sighting/137520874</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136795161</v>
+        <v>136798692</v>
       </c>
       <c r="B18" t="n">
-        <v>58191</v>
+        <v>58196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513993</v>
+        <v>514162</v>
       </c>
       <c r="R18" t="n">
-        <v>6757411</v>
+        <v>6757515</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,22 +2580,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,27 +2610,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795161</t>
+          <t>https://artportalen.se/Sighting/136798692</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136798682</v>
+        <v>136795161</v>
       </c>
       <c r="B19" t="n">
-        <v>8470</v>
+        <v>58191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,21 +2638,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,13 +2662,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514058</v>
+        <v>513993</v>
       </c>
       <c r="R19" t="n">
-        <v>6757263</v>
+        <v>6757411</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2687,22 +2692,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,27 +2722,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798682</t>
+          <t>https://artportalen.se/Sighting/136795161</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837973</v>
+        <v>136798682</v>
       </c>
       <c r="B20" t="n">
-        <v>8444</v>
+        <v>8470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2745,21 +2750,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,13 +2774,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514178</v>
+        <v>514058</v>
       </c>
       <c r="R20" t="n">
-        <v>6757557</v>
+        <v>6757263</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,12 +2804,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,27 +2834,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837973</t>
+          <t>https://artportalen.se/Sighting/136798682</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126837950</v>
+        <v>137520872</v>
       </c>
       <c r="B21" t="n">
-        <v>99153</v>
+        <v>8470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,37 +2862,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Born1, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514178</v>
+        <v>514119</v>
       </c>
       <c r="R21" t="n">
-        <v>6757313</v>
+        <v>6757552</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2901,12 +2916,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Torrtall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,27 +2951,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837950</t>
+          <t>https://artportalen.se/Sighting/137520872</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136936654</v>
+        <v>126837973</v>
       </c>
       <c r="B22" t="n">
-        <v>99469</v>
+        <v>8444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,45 +2979,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513908</v>
+        <v>514178</v>
       </c>
       <c r="R22" t="n">
-        <v>6757597</v>
+        <v>6757557</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3011,12 +3033,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,60 +3047,55 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malin Schött</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136936654</t>
+          <t>https://artportalen.se/Sighting/126837973</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126837967</v>
+        <v>126837950</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3105,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514171</v>
+        <v>514178</v>
       </c>
       <c r="R23" t="n">
-        <v>6757320</v>
+        <v>6757313</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,63 +3166,62 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837967</t>
+          <t>https://artportalen.se/Sighting/126837950</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132008521</v>
+        <v>136936654</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514007</v>
+        <v>513908</v>
       </c>
       <c r="R24" t="n">
-        <v>6757453</v>
+        <v>6757597</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,22 +3245,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,33 +3259,38 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008521</t>
+          <t>https://artportalen.se/Sighting/136936654</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132009294</v>
+        <v>126837967</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,26 +3315,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514154</v>
+        <v>514171</v>
       </c>
       <c r="R25" t="n">
-        <v>6757482</v>
+        <v>6757320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3350,22 +3352,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3380,24 +3372,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009294</t>
+          <t>https://artportalen.se/Sighting/126837967</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132009740</v>
+        <v>132008521</v>
       </c>
       <c r="B26" t="n">
         <v>99195</v>
@@ -3427,7 +3419,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3436,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514174</v>
+        <v>514007</v>
       </c>
       <c r="R26" t="n">
-        <v>6757543</v>
+        <v>6757453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3481,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,13 +3504,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009740</t>
+          <t>https://artportalen.se/Sighting/132008521</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132010406</v>
+        <v>132009294</v>
       </c>
       <c r="B27" t="n">
         <v>99195</v>
@@ -3543,7 +3540,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3557,10 +3554,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514098</v>
+        <v>514154</v>
       </c>
       <c r="R27" t="n">
-        <v>6757561</v>
+        <v>6757482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3592,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3602,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,13 +3625,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132010406</t>
+          <t>https://artportalen.se/Sighting/132009294</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132012536</v>
+        <v>132009740</v>
       </c>
       <c r="B28" t="n">
         <v>99195</v>
@@ -3664,12 +3661,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3678,10 +3670,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514113</v>
+        <v>514174</v>
       </c>
       <c r="R28" t="n">
-        <v>6757269</v>
+        <v>6757543</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3713,7 +3705,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3723,7 +3715,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,13 +3741,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132012536</t>
+          <t>https://artportalen.se/Sighting/132009740</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132013322</v>
+        <v>132010406</v>
       </c>
       <c r="B29" t="n">
         <v>99195</v>
@@ -3783,17 +3775,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513994</v>
+        <v>514098</v>
       </c>
       <c r="R29" t="n">
-        <v>6757319</v>
+        <v>6757561</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3825,7 +3826,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3835,7 +3836,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3861,16 +3862,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132013322</t>
+          <t>https://artportalen.se/Sighting/132010406</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136795149</v>
+        <v>132012536</v>
       </c>
       <c r="B30" t="n">
-        <v>99418</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,7 +3898,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3907,17 +3908,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514167</v>
+        <v>514113</v>
       </c>
       <c r="R30" t="n">
-        <v>6757542</v>
+        <v>6757269</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3941,22 +3942,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,27 +3972,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795149</t>
+          <t>https://artportalen.se/Sighting/132012536</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136795151</v>
+        <v>132013322</v>
       </c>
       <c r="B31" t="n">
-        <v>99418</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4016,29 +4017,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514179</v>
+        <v>513994</v>
       </c>
       <c r="R31" t="n">
-        <v>6757570</v>
+        <v>6757319</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,22 +4054,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,24 +4084,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795151</t>
+          <t>https://artportalen.se/Sighting/132013322</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136798685</v>
+        <v>136795149</v>
       </c>
       <c r="B32" t="n">
         <v>99418</v>
@@ -4139,7 +4131,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4147,19 +4139,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514094</v>
+        <v>514167</v>
       </c>
       <c r="R32" t="n">
-        <v>6757495</v>
+        <v>6757542</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4186,27 +4175,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>4 blomställningar 4 bladroserrer</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4215,31 +4199,30 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798685</t>
+          <t>https://artportalen.se/Sighting/136795149</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136798686</v>
+        <v>136795151</v>
       </c>
       <c r="B33" t="n">
         <v>99418</v>
@@ -4267,20 +4250,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514118</v>
+        <v>514179</v>
       </c>
       <c r="R33" t="n">
-        <v>6757538</v>
+        <v>6757570</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4304,27 +4296,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 blom 6 blad</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4339,24 +4326,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798686</t>
+          <t>https://artportalen.se/Sighting/136795151</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136798687</v>
+        <v>136798685</v>
       </c>
       <c r="B34" t="n">
         <v>99418</v>
@@ -4386,10 +4373,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4399,10 +4390,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514114</v>
+        <v>514094</v>
       </c>
       <c r="R34" t="n">
-        <v>6757542</v>
+        <v>6757495</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4434,7 +4425,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4444,12 +4435,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 överblommade ståndare 15 bladrosetter</t>
+          <t>4 blomställningar 4 bladroserrer</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,13 +4467,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798687</t>
+          <t>https://artportalen.se/Sighting/136798685</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136798689</v>
+        <v>136798686</v>
       </c>
       <c r="B35" t="n">
         <v>99418</v>
@@ -4510,28 +4501,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514173</v>
+        <v>514118</v>
       </c>
       <c r="R35" t="n">
-        <v>6757591</v>
+        <v>6757538</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4560,7 +4543,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4570,12 +4553,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 böadrosetter</t>
+          <t>2 blom 6 blad</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,7 +4567,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4602,13 +4584,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798689</t>
+          <t>https://artportalen.se/Sighting/136798686</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136798690</v>
+        <v>136798687</v>
       </c>
       <c r="B36" t="n">
         <v>99418</v>
@@ -4638,7 +4620,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -4651,10 +4633,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514168</v>
+        <v>514114</v>
       </c>
       <c r="R36" t="n">
-        <v>6757541</v>
+        <v>6757542</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4686,7 +4668,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4696,12 +4678,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>2 överblommade ståndare 15 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4728,13 +4710,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798690</t>
+          <t>https://artportalen.se/Sighting/136798687</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136798691</v>
+        <v>136798689</v>
       </c>
       <c r="B37" t="n">
         <v>99418</v>
@@ -4764,7 +4746,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4777,13 +4759,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514161</v>
+        <v>514173</v>
       </c>
       <c r="R37" t="n">
-        <v>6757513</v>
+        <v>6757591</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4812,7 +4794,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4822,12 +4804,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>4 böadrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4854,13 +4836,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798691</t>
+          <t>https://artportalen.se/Sighting/136798689</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136798693</v>
+        <v>136798690</v>
       </c>
       <c r="B38" t="n">
         <v>99418</v>
@@ -4890,14 +4872,10 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4907,10 +4885,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514153</v>
+        <v>514168</v>
       </c>
       <c r="R38" t="n">
-        <v>6757506</v>
+        <v>6757541</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4942,7 +4920,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4952,12 +4930,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>100st på 2 m2</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4984,13 +4962,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798693</t>
+          <t>https://artportalen.se/Sighting/136798690</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136798694</v>
+        <v>136798691</v>
       </c>
       <c r="B39" t="n">
         <v>99418</v>
@@ -5018,20 +4996,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514120</v>
+        <v>514161</v>
       </c>
       <c r="R39" t="n">
-        <v>6757531</v>
+        <v>6757513</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5055,27 +5041,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5084,6 +5070,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5101,13 +5088,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798694</t>
+          <t>https://artportalen.se/Sighting/136798691</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136798695</v>
+        <v>136798693</v>
       </c>
       <c r="B40" t="n">
         <v>99418</v>
@@ -5135,8 +5122,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -5145,13 +5141,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514133</v>
+        <v>514153</v>
       </c>
       <c r="R40" t="n">
-        <v>6757538</v>
+        <v>6757506</v>
       </c>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5175,22 +5171,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>100st på 2 m2</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5217,13 +5218,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798695</t>
+          <t>https://artportalen.se/Sighting/136798693</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136798696</v>
+        <v>136798694</v>
       </c>
       <c r="B41" t="n">
         <v>99418</v>
@@ -5251,28 +5252,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514133</v>
+        <v>514120</v>
       </c>
       <c r="R41" t="n">
-        <v>6757547</v>
+        <v>6757531</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5301,7 +5294,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5311,7 +5304,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5320,7 +5318,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5338,13 +5335,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798696</t>
+          <t>https://artportalen.se/Sighting/136798694</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136798697</v>
+        <v>136798695</v>
       </c>
       <c r="B42" t="n">
         <v>99418</v>
@@ -5372,17 +5369,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5391,13 +5379,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514145</v>
+        <v>514133</v>
       </c>
       <c r="R42" t="n">
-        <v>6757586</v>
+        <v>6757538</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5426,7 +5414,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5436,12 +5424,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>15 badrosetter</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5468,54 +5451,62 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798697</t>
+          <t>https://artportalen.se/Sighting/136798695</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136795154</v>
+        <v>136798696</v>
       </c>
       <c r="B43" t="n">
-        <v>103999</v>
+        <v>99418</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513942</v>
+        <v>514133</v>
       </c>
       <c r="R43" t="n">
-        <v>6757692</v>
+        <v>6757547</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5544,7 +5535,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5554,7 +5545,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5563,71 +5554,84 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795154</t>
+          <t>https://artportalen.se/Sighting/136798696</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136795156</v>
+        <v>136798697</v>
       </c>
       <c r="B44" t="n">
-        <v>103999</v>
+        <v>99418</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513937</v>
+        <v>514145</v>
       </c>
       <c r="R44" t="n">
-        <v>6757667</v>
+        <v>6757586</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5656,7 +5660,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5666,7 +5670,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>15 badrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5675,71 +5684,72 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795156</t>
+          <t>https://artportalen.se/Sighting/136798697</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136795157</v>
+        <v>137520871</v>
       </c>
       <c r="B45" t="n">
-        <v>103999</v>
+        <v>99435</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Born1, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513908</v>
+        <v>514124</v>
       </c>
       <c r="R45" t="n">
-        <v>6757637</v>
+        <v>6757542</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5763,22 +5773,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Blandbarrskog 100 +</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5793,27 +5808,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795157</t>
+          <t>https://artportalen.se/Sighting/137520871</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126837934</v>
+        <v>136795154</v>
       </c>
       <c r="B46" t="n">
-        <v>104628</v>
+        <v>103999</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5821,16 +5836,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5845,13 +5860,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514224</v>
+        <v>513942</v>
       </c>
       <c r="R46" t="n">
-        <v>6757306</v>
+        <v>6757692</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5875,12 +5890,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5895,27 +5920,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837934</t>
+          <t>https://artportalen.se/Sighting/136795154</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126837969</v>
+        <v>136795156</v>
       </c>
       <c r="B47" t="n">
-        <v>101326</v>
+        <v>103999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5923,21 +5948,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5947,13 +5972,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514019</v>
+        <v>513937</v>
       </c>
       <c r="R47" t="n">
-        <v>6757359</v>
+        <v>6757667</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5977,12 +6002,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5997,27 +6032,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837969</t>
+          <t>https://artportalen.se/Sighting/136795156</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126837972</v>
+        <v>136795157</v>
       </c>
       <c r="B48" t="n">
-        <v>101326</v>
+        <v>103999</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,21 +6060,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6049,13 +6084,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514153</v>
+        <v>513908</v>
       </c>
       <c r="R48" t="n">
-        <v>6757646</v>
+        <v>6757637</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6079,12 +6114,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6099,27 +6144,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126837972</t>
+          <t>https://artportalen.se/Sighting/136795157</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132008409</v>
+        <v>126837934</v>
       </c>
       <c r="B49" t="n">
-        <v>101403</v>
+        <v>104628</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6127,43 +6172,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514007</v>
+        <v>514224</v>
       </c>
       <c r="R49" t="n">
-        <v>6757453</v>
+        <v>6757306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6190,22 +6226,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6220,27 +6246,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132008409</t>
+          <t>https://artportalen.se/Sighting/126837934</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132009025</v>
+        <v>126837969</v>
       </c>
       <c r="B50" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,21 +6291,17 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514069</v>
+        <v>514019</v>
       </c>
       <c r="R50" t="n">
-        <v>6757477</v>
+        <v>6757359</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6306,22 +6328,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,27 +6348,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132009025</t>
+          <t>https://artportalen.se/Sighting/126837969</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132013399</v>
+        <v>126837972</v>
       </c>
       <c r="B51" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,14 +6396,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lintjärnen, Dlr</t>
+          <t>Born, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513994</v>
+        <v>514153</v>
       </c>
       <c r="R51" t="n">
-        <v>6757319</v>
+        <v>6757646</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6418,22 +6430,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6448,27 +6450,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132013399</t>
+          <t>https://artportalen.se/Sighting/126837972</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136795145</v>
+        <v>132008409</v>
       </c>
       <c r="B52" t="n">
-        <v>101634</v>
+        <v>101403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6493,20 +6495,29 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514123</v>
+        <v>514007</v>
       </c>
       <c r="R52" t="n">
-        <v>6757409</v>
+        <v>6757453</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6530,22 +6541,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6560,27 +6571,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795145</t>
+          <t>https://artportalen.se/Sighting/132008409</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136795152</v>
+        <v>132009025</v>
       </c>
       <c r="B53" t="n">
-        <v>101634</v>
+        <v>101403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,20 +6616,24 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514149</v>
+        <v>514069</v>
       </c>
       <c r="R53" t="n">
-        <v>6757621</v>
+        <v>6757477</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6642,22 +6657,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6672,27 +6687,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795152</t>
+          <t>https://artportalen.se/Sighting/132009025</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136795158</v>
+        <v>132013399</v>
       </c>
       <c r="B54" t="n">
-        <v>101634</v>
+        <v>101403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6720,14 +6735,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Born, Dlr</t>
+          <t>Lintjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513852</v>
+        <v>513994</v>
       </c>
       <c r="R54" t="n">
-        <v>6757553</v>
+        <v>6757319</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6754,22 +6769,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6784,24 +6799,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136795158</t>
+          <t>https://artportalen.se/Sighting/132013399</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136798683</v>
+        <v>136795145</v>
       </c>
       <c r="B55" t="n">
         <v>101634</v>
@@ -6836,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514083</v>
+        <v>514123</v>
       </c>
       <c r="R55" t="n">
-        <v>6757414</v>
+        <v>6757409</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6866,22 +6881,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6896,24 +6911,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798683</t>
+          <t>https://artportalen.se/Sighting/136795145</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136798688</v>
+        <v>136795152</v>
       </c>
       <c r="B56" t="n">
         <v>101634</v>
@@ -6948,10 +6963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514125</v>
+        <v>514149</v>
       </c>
       <c r="R56" t="n">
-        <v>6757625</v>
+        <v>6757621</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6978,22 +6993,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7008,24 +7023,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798688</t>
+          <t>https://artportalen.se/Sighting/136795152</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136798698</v>
+        <v>136795158</v>
       </c>
       <c r="B57" t="n">
         <v>101634</v>
@@ -7060,13 +7075,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>514148</v>
+        <v>513852</v>
       </c>
       <c r="R57" t="n">
-        <v>6757596</v>
+        <v>6757553</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7095,7 +7110,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7105,7 +7120,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7120,24 +7135,24 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136798698</t>
+          <t>https://artportalen.se/Sighting/136795158</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136799092</v>
+        <v>136798683</v>
       </c>
       <c r="B58" t="n">
         <v>101634</v>
@@ -7172,10 +7187,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513831</v>
+        <v>514083</v>
       </c>
       <c r="R58" t="n">
-        <v>6757584</v>
+        <v>6757414</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7202,22 +7217,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7237,22 +7252,22 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799092</t>
+          <t>https://artportalen.se/Sighting/136798683</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136799212</v>
+        <v>136798688</v>
       </c>
       <c r="B59" t="n">
-        <v>99224</v>
+        <v>101634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7260,21 +7275,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7284,10 +7299,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513868</v>
+        <v>514125</v>
       </c>
       <c r="R59" t="n">
-        <v>6757642</v>
+        <v>6757625</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7314,22 +7329,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7349,22 +7364,22 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799212</t>
+          <t>https://artportalen.se/Sighting/136798688</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136799215</v>
+        <v>136798698</v>
       </c>
       <c r="B60" t="n">
-        <v>99224</v>
+        <v>101634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7372,21 +7387,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7396,13 +7411,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513929</v>
+        <v>514148</v>
       </c>
       <c r="R60" t="n">
-        <v>6757710</v>
+        <v>6757596</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7426,22 +7441,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7461,11 +7476,347 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136798698</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136799092</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101634</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>513831</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6757584</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799092</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136799212</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99224</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>513868</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6757642</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799212</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136799215</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99224</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Born, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>513929</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6757710</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136799215</t>
         </is>
@@ -7532,6 +7883,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35453-2026 artfynd.xlsx
+++ b/artfynd/A 35453-2026 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136933180</v>
       </c>
       <c r="B3" t="n">
-        <v>99341</v>
+        <v>99344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>137520874</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>136936654</v>
       </c>
       <c r="B24" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>137520871</v>
       </c>
       <c r="B45" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
